--- a/Configs/GameConfig/Datas/fg/#TerritoryTemplate-领地模板.xlsx
+++ b/Configs/GameConfig/Datas/fg/#TerritoryTemplate-领地模板.xlsx
@@ -958,7 +958,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>terminal.lore.silent.a,terminal.lore.silent.b,terminal.lore.silent.c</t>
+          <t>terminal.lore.silent.a,terminal.lore.silent.b,terminal.lore.silent.c,terminal.lore.silent.d,terminal.lore.silent.e</t>
         </is>
       </c>
       <c r="AA4" t="n">
